--- a/data/gravel/Giant Revolt pro (long) 2025.xlsx
+++ b/data/gravel/Giant Revolt pro (long) 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10824"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B99CB18F-D962-CD4B-BCC2-03E4BD78C230}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A57A4E5-A37C-D044-A476-43F54E3D14C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1780" yWindow="500" windowWidth="26480" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25660" yWindow="-20980" windowWidth="31040" windowHeight="19680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="133">
   <si>
     <t>brand</t>
   </si>
@@ -1129,9 +1129,6 @@
   </si>
   <si>
     <t>flip</t>
-  </si>
-  <si>
-    <t>`</t>
   </si>
   <si>
     <t>Revolt Advanced Pro (long)</t>
@@ -1545,7 +1542,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
@@ -1911,28 +1908,28 @@
         <v>118</v>
       </c>
       <c r="C15" s="5">
-        <f>VALUE(RIGHT(J15,2))</f>
-        <v>82</v>
+        <f>VALUE(LEFT(J15,2))</f>
+        <v>78</v>
       </c>
       <c r="D15" s="5">
-        <f t="shared" ref="D15:H15" si="0">VALUE(RIGHT(K15,2))</f>
-        <v>75</v>
+        <f t="shared" ref="D15:H15" si="0">VALUE(LEFT(K15,2))</f>
+        <v>72</v>
       </c>
       <c r="E15" s="5">
         <f t="shared" si="0"/>
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="F15" s="5">
         <f t="shared" si="0"/>
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="G15" s="5">
         <f t="shared" si="0"/>
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H15" s="5">
         <f t="shared" si="0"/>
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="J15" s="5" t="s">
         <v>93</v>
@@ -2249,6 +2246,7 @@
         <v>125</v>
       </c>
       <c r="C22" s="5">
+        <f t="shared" ref="C22:C24" si="5">VALUE(RIGHT(J22,3))</f>
         <v>420</v>
       </c>
       <c r="D22" s="5">
@@ -2293,6 +2291,7 @@
         <v>126</v>
       </c>
       <c r="C23" s="5">
+        <f t="shared" si="5"/>
         <v>50</v>
       </c>
       <c r="D23" s="5">
@@ -2337,6 +2336,7 @@
         <v>127</v>
       </c>
       <c r="C24" s="5">
+        <f t="shared" si="5"/>
         <v>170</v>
       </c>
       <c r="D24" s="5">
@@ -2498,19 +2498,19 @@
         <v>157.5</v>
       </c>
       <c r="E30">
-        <f t="shared" ref="E30:H30" si="5">AVERAGE(E32,D33)</f>
+        <f t="shared" ref="E30:H30" si="6">AVERAGE(E32,D33)</f>
         <v>170</v>
       </c>
       <c r="F30">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>177.5</v>
       </c>
       <c r="G30">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>182.5</v>
       </c>
       <c r="H30">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>190</v>
       </c>
     </row>
@@ -2526,19 +2526,19 @@
         <v>157.5</v>
       </c>
       <c r="D31">
-        <f t="shared" ref="D31:G31" si="6">E30</f>
+        <f t="shared" ref="D31:G31" si="7">E30</f>
         <v>170</v>
       </c>
       <c r="E31">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>177.5</v>
       </c>
       <c r="F31">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>182.5</v>
       </c>
       <c r="G31">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>190</v>
       </c>
       <c r="H31">
@@ -2652,8 +2652,8 @@
       <c r="A42" t="s">
         <v>43</v>
       </c>
-      <c r="B42" s="1" t="s">
-        <v>132</v>
+      <c r="B42">
+        <v>53</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">

--- a/data/gravel/Giant Revolt pro (long) 2025.xlsx
+++ b/data/gravel/Giant Revolt pro (long) 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10824"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A57A4E5-A37C-D044-A476-43F54E3D14C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EF528E6-BE1A-1748-8EF6-D558DA8C6A7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25660" yWindow="-20980" windowWidth="31040" windowHeight="19680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2540" yWindow="5660" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="136">
   <si>
     <t>brand</t>
   </si>
@@ -1128,10 +1128,19 @@
     <t>a8:h33</t>
   </si>
   <si>
-    <t>flip</t>
-  </si>
-  <si>
     <t>Revolt Advanced Pro (long)</t>
+  </si>
+  <si>
+    <t>https://www.giant-bicycles.com/us/revolt-advanced-pro-1</t>
+  </si>
+  <si>
+    <t>https://images2.giant-bicycles.com/b_white%2Cc_pad%2Ch_850%2Cq_80/nu50syqftgvwjxg8dlia/MY25RevoltAdvancedPro1_ColorAMeteorStorm.jpg</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>± 10</t>
   </si>
 </sst>
 </file>
@@ -1542,7 +1551,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
@@ -1565,6 +1574,14 @@
       <c r="A5" t="s">
         <v>5</v>
       </c>
+      <c r="B5" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
@@ -2645,7 +2662,7 @@
         <v>42</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
@@ -2843,6 +2860,9 @@
       <c r="A71" t="s">
         <v>72</v>
       </c>
+      <c r="B71">
+        <v>5000</v>
+      </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
@@ -2852,6 +2872,9 @@
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>74</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>134</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Giant Revolt pro (long) 2025.xlsx
+++ b/data/gravel/Giant Revolt pro (long) 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EF528E6-BE1A-1748-8EF6-D558DA8C6A7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBF84BDA-B234-B44F-81ED-6FD9D4ECEEF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2540" yWindow="5660" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10280" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="138">
   <si>
     <t>brand</t>
   </si>
@@ -1141,6 +1141,12 @@
   </si>
   <si>
     <t>± 10</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Dajia, Taichung, Taiwan</t>
   </si>
 </sst>
 </file>
@@ -1532,7 +1538,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O73"/>
+  <dimension ref="A1:O74"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -2877,6 +2883,14 @@
         <v>134</v>
       </c>
     </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>136</v>
+      </c>
+      <c r="B74" t="s">
+        <v>137</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/gravel/Giant Revolt pro (long) 2025.xlsx
+++ b/data/gravel/Giant Revolt pro (long) 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBF84BDA-B234-B44F-81ED-6FD9D4ECEEF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00A7F028-77F7-174D-B587-F59458A51955}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10280" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="144">
   <si>
     <t>brand</t>
   </si>
@@ -1147,6 +1147,24 @@
   </si>
   <si>
     <t>Dajia, Taichung, Taiwan</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -1538,7 +1556,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O74"/>
+  <dimension ref="A1:O80"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -2722,172 +2740,202 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>51</v>
-      </c>
-      <c r="B50" s="1"/>
+        <v>138</v>
+      </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>52</v>
+        <v>139</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>53</v>
-      </c>
-      <c r="B52">
-        <v>30.9</v>
+        <v>140</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>54</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>55</v>
+        <v>142</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>56</v>
+        <v>143</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>57</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="B56" s="1"/>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>59</v>
+        <v>53</v>
+      </c>
+      <c r="B58">
+        <v>30.9</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>61</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>128</v>
+        <v>55</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>63</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>129</v>
+        <v>57</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>64</v>
-      </c>
-      <c r="B63">
-        <v>2</v>
+        <v>58</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>65</v>
-      </c>
-      <c r="B64">
-        <v>1</v>
+        <v>59</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>66</v>
-      </c>
-      <c r="B65">
-        <v>1</v>
+        <v>60</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>68</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>129</v>
+        <v>62</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>69</v>
+        <v>63</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>70</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>129</v>
+        <v>64</v>
+      </c>
+      <c r="B69">
+        <v>2</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="B70">
-        <v>2300</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="B71">
-        <v>5000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>73</v>
+        <v>67</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>70</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>71</v>
+      </c>
+      <c r="B76">
+        <v>2300</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>72</v>
+      </c>
+      <c r="B77">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>74</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
         <v>136</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B80" t="s">
         <v>137</v>
       </c>
     </row>
